--- a/KONSTRYX_Status_Tracker.xlsx
+++ b/KONSTRYX_Status_Tracker.xlsx
@@ -94,12 +94,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -4967,7 +4967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5033,54 +5033,54 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Q-01</t>
+          <t>Q-15</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Document number ranges: per company or group-global?</t>
+          <t>Starter content pack: ship it, or only on a demo tenant?</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED: configurable per object. Built and verified both scopes</t>
+          <t>KONSTRYX ships masters, a sample project and the canonical RR thread to every tenant. Useful on an evaluation tenant in front of a starter S/4; actively harmful on a customer system, where it puts rows nothing can cleanly remove and - now that release pushes on its own - possibly documents in their S/4. Three shipped-data failures this build all reduce to the same disease: the pack asserted a relationship with a system it had never seen</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Detect a starter system / declare a contentProfile at subscription (recommended, default CLEAN) / ask on first run. Detection rejected: inferring it from company code 1710 is the same species of guess that produced the profit-centre bug. See docs/ARCHITECTURE_TENANT_CONTENT.md</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Content pack strategy; whether demo content needs to be removable at all</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Answered 2026-08-15</t>
+          <t>Before the first customer tenant</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Q-13</t>
+          <t>Q-01</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Where does KONSTRYX surface — Work Zone or the S/4 launchpad?</t>
+          <t>Document number ranges: per company or group-global?</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED: Option A, S/4's own launchpad. See D-16</t>
+          <t>ANSWERED: configurable per object. Built and verified both scopes</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -5093,7 +5093,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -5107,17 +5107,17 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-13</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Does numbering need to be gap-free for audit?</t>
+          <t>Where does KONSTRYX surface — Work Zone or the S/4 launchpad?</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED 2026-08-17: gaps are acceptable provided a valid audit log is available — a cancelled document leaving a gap is fine. Current behaviour (numbers issued on activation, abandoned drafts consume nothing) therefore stands; the audit log is the control, not the sequence</t>
+          <t>ANSWERED: Option A, S/4's own launchpad. See D-16</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -5130,31 +5130,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Answered 2026-08-17</t>
+          <t>Answered 2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Q-02</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>What is in the EC&amp;O starter content pack?</t>
+          <t>Does numbering need to be gap-free for audit?</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED 2026-08-17: the masters and a sample transaction exactly as they appear in the wireframe today, end to end and demo-ready — not a curated subset. The wireframe's own data is the pack</t>
+          <t>ANSWERED 2026-08-17: gaps are acceptable provided a valid audit log is available — a cancelled document leaving a gap is fine. Current behaviour (numbers issued on activation, abandoned drafts consume nothing) therefore stands; the audit log is the control, not the sequence</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -5167,7 +5167,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -5181,17 +5181,17 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Q-03</t>
+          <t>Q-02</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Approval schemes: who approves what, at which value bands?</t>
+          <t>What is in the EC&amp;O starter content pack?</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED 2026-08-17: confirmed — keep the shipped thresholds (Budget 100k/1m, Resource Request 250k/1m) as they stand. Approver personas remain unnamed and configurable in-app</t>
+          <t>ANSWERED 2026-08-17: the masters and a sample transaction exactly as they appear in the wireframe today, end to end and demo-ready — not a curated subset. The wireframe's own data is the pack</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -5204,7 +5204,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -5218,17 +5218,17 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Q-04</t>
+          <t>Q-03</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Attachment storage: SAP Object Store or HANA LOB?</t>
+          <t>Approval schemes: who approves what, at which value bands?</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED 2026-08-17: neither as a fixed choice — attachments get a configuration that can point at any DMS. Storage becomes a per-tenant setting rather than a build-time decision, which supersedes the Object Store vs HANA LOB framing</t>
+          <t>ANSWERED 2026-08-17: confirmed — keep the shipped thresholds (Budget 100k/1m, Resource Request 250k/1m) as they stand. Approver personas remain unnamed and configurable in-app</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -5238,10 +5238,10 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>F-04 — needs rework to a configurable DMS target</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -5255,17 +5255,17 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Q-05</t>
+          <t>Q-04</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>The canonical demo numbers do not reconcile</t>
+          <t>Attachment storage: SAP Object Store or HANA LOB?</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED 2026-08-17: correct the header to 685,080 — the line values and the per-WBS commitment split are right, the header was wrong. The L1 rate question falls away with it</t>
+          <t>ANSWERED 2026-08-17: neither as a fixed choice — attachments get a configuration that can point at any DMS. Storage becomes a per-tenant setting rather than a build-time decision, which supersedes the Object Store vs HANA LOB framing</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -5275,10 +5275,10 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
+          <t>F-04 — needs rework to a configurable DMS target</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -5292,17 +5292,17 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>Q-05</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>BOQ import template — confirm the column set</t>
+          <t>The canonical demo numbers do not reconcile</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED 2026-08-17: there is no single template to build to. Bills arrive from different estimating tools — Candy, RAI and others — so the importer must be flexible: a mappable column set per source rather than one fixed contract. This changes the shape of B-04, which was scoped to import a known template</t>
+          <t>ANSWERED 2026-08-17: correct the header to 685,080 — the line values and the per-WBS commitment split are right, the header was wrong. The L1 rate question falls away with it</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -5312,10 +5312,10 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>B-04 Uploads — needs rescoping to a per-source column mapping</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -5329,257 +5329,294 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBS instance versioning: copy-on-create or live reference to the library?</t>
+          <t>BOQ import template — confirm the column set</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Open item in Data Model Spec section 10. Affects whether library changes propagate into running projects</t>
+          <t>ANSWERED 2026-08-17: there is no single template to build to. Bills arrive from different estimating tools — Candy, RAI and others — so the importer must be flexible: a mappable column set per source rather than one fixed contract. This changes the shape of B-04, which was scoped to import a known template</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Copy-on-create (proposed) / live reference</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>B-01, B-03</t>
+          <t>B-04 Uploads — needs rescoping to a per-source column mapping</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Before Project Setup</t>
+          <t>Answered 2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Encumbrance currency: company currency or group reporting currency?</t>
+          <t>CBS instance versioning: copy-on-create or live reference to the library?</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED 2026-08-17: both — the encumbrance is held in company currency and also carried at group reporting currency, not one or the other. Budget lines and ledger entries are single-currency today, so this needs a second amount (or a conversion at read) before group-level budget reporting is honest</t>
+          <t>Open item in Data Model Spec section 10. Affects whether library changes propagate into running projects</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Copy-on-create (proposed) / live reference</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>B-06 Budgeting — the budget ledger carries one amount today; dual currency is not built</t>
+          <t>B-01, B-03</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Answered 2026-08-17</t>
+          <t>Before Project Setup</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Q-09p</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>S/4 sandbox tenant - RESOLVED for projects</t>
+          <t>Encumbrance currency: company currency or group reporting currency?</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Communication user + arrangements SAP_COM_0308/0008 active. The connector ran live: KX-S4-001 created in the tenant from KONSTRYX through release -&gt; sync, confirmed by an independent read (profile YP05). WBS element read-back also confirmed: A_EnterpriseProject is keyed by ProjectUUID (a GUID), not the Project string — once read with the correct key, to_EnterpriseProjectElement returns both elements (the auto-created root KX-S4-001 and the pushed KX-S4-001.1 'Enabling works'). Remaining: the other scenarios (procurement, finance) as their modules need them</t>
+          <t>ANSWERED 2026-08-17: both — the encumbrance is held in company currency and also carried at group reporting currency, not one or the other. Budget lines and ledger entries are single-currency today, so this needs a second amount (or a conversion at read) before group-level budget reporting is honest</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Rotate the credential that transited chat transcripts when convenient; move to a BTP destination at deployment</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>S/4 connector - project scenario DONE, incl. WBS read-back</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+          <t>B-06 Budgeting — the budget ledger carries one amount today; dual currency is not built</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>Answered 2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>Q-09p</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>S/4 dev tenant — what is actually needed (merges the old S-15)</t>
+          <t>S/4 sandbox tenant - RESOLVED for projects</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ANSWERED 2026-08-17: already shared — the sandbox tenant with its communication user, and SAP_COM_0308/0008 active. Proven live by the project connector (see Q-09p). What remains is per-scenario, not per-tenant: the procurement arrangements (SAP_COM_0053 for the requisition, SAP_COM_0193 for the order) need activating before the PR push can be tested</t>
+          <t>Communication user + arrangements SAP_COM_0308/0008 active. The connector ran live: KX-S4-001 created in the tenant from KONSTRYX through release -&gt; sync, confirmed by an independent read (profile YP05). WBS element read-back also confirmed: A_EnterpriseProject is keyed by ProjectUUID (a GUID), not the Project string — once read with the correct key, to_EnterpriseProjectElement returns both elements (the auto-created root KX-S4-001 and the pushed KX-S4-001.1 'Enabling works'). Remaining: the other scenarios (procurement, finance) as their modules need them</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rotate the credential that transited chat transcripts when convenient; move to a BTP destination at deployment</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Project sync done; procurement arrangements still to activate</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
+          <t>S/4 connector - project scenario DONE, incl. WBS read-back</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Answered 2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Q-10</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Scope re-baseline: personalization + attachments + approvals on every screen</t>
+          <t>S/4 dev tenant — what is actually needed (merges the old S-15)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Wireframe v12 is 41 modules / 434 screens. The 22-week MVP plan with 1 UI5 developer does not carry this</t>
+          <t>ANSWERED 2026-08-17: already shared — the sandbox tenant with its communication user, and SAP_COM_0308/0008 active. Proven live by the project connector (see Q-09p). What remains is per-scenario, not per-tenant: the procurement arrangements (SAP_COM_0053 for the requisition, SAP_COM_0193 for the order) need activating before the PR push can be tested</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Re-baseline the plan / reduce MVP screen scope / add UI capacity</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Overall plan credibility</t>
+          <t>Project sync done; procurement arrangements still to activate</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Before committing a client date</t>
+          <t>Answered 2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Q-11</t>
+          <t>Q-10</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>UI5 production delivery: how is the app served in Cloud Foundry?</t>
+          <t>Scope re-baseline: personalization + attachments + approvals on every screen</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>mta.yaml has no approuter and no UI module today, and the app bootstraps from a local runtime path</t>
+          <t>Wireframe v12 is 41 modules / 434 screens. The 22-week MVP plan with 1 UI5 developer does not carry this</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Approuter + HTML5 repo (standard) / other</t>
+          <t>Re-baseline the plan / reduce MVP screen scope / add UI capacity</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
+          <t>Overall plan credibility</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Before first CF deploy</t>
+          <t>Before committing a client date</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>Q-11</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>UI5 production delivery: how is the app served in Cloud Foundry?</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>mta.yaml has no approuter and no UI module today, and the app bootstraps from a local runtime path</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Approuter + HTML5 repo (standard) / other</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Before first CF deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>Q-12</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>CI/CD tooling</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Prerequisite 4 in the phase plan, still undecided</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>SAP CI/CD service / GitHub Actions / Azure DevOps</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>D-03</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Before team scales up</t>
         </is>
@@ -6123,7 +6160,7 @@
           <t>Re-baseline before any client date is committed, or cut MVP screen scope</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6160,7 +6197,7 @@
           <t>Revisit at 5-10 clients; decide before the first go-live, not after</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6197,7 +6234,7 @@
           <t>Split as screens are built; register an intent per app</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6234,7 +6271,7 @@
           <t>Move when the app splits into several apps</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6271,7 +6308,7 @@
           <t>Add a startup check over the catalogue against the model</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6308,7 +6345,7 @@
           <t>Make H2 file-backed, or point local dev at HANA Cloud, before any live demo</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6345,7 +6382,7 @@
           <t>Add it to the build script or CI pipeline</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6419,7 +6456,7 @@
           <t>Correct the header, or supply the intended numbers</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6456,7 +6493,7 @@
           <t>Confirm per document type; some jurisdictions require unbroken sequences</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6493,7 +6530,7 @@
           <t>Keep blocking unless the business prefers a merge; it is a one-method change</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6530,7 +6567,7 @@
           <t>Security review of both layers before the first client</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6567,7 +6604,7 @@
           <t>Ship the EC&amp;O starter pack the same way</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6604,7 +6641,7 @@
           <t>Build it before Templates so the pattern is settled once</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
@@ -6678,7 +6715,7 @@
           <t>Restate the rule in the product documentation so the exception is deliberate rather than remembered</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6715,7 +6752,7 @@
           <t>Show the unsynchronised state prominently in the UI and block budget release until the S/4 project exists</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6789,7 +6826,7 @@
           <t>Replace them before any client sees the product. See Q-03</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6826,7 +6863,7 @@
           <t>Confirm the default is right for EC&amp;O clients; it is a per-step switch either way</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6863,7 +6900,7 @@
           <t>Decide per object type whether an edit invalidates an in-flight or completed approval; wire it with F-05</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6900,7 +6937,7 @@
           <t>Confirm the intended behaviour: should a scheme edit affect approvals already running? Today it partly does</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6937,7 +6974,7 @@
           <t>Answer OPEN-01 and OPEN-02 in the spec; the roll-up is a one-day build once pinned</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6974,7 +7011,7 @@
           <t>Decide where the role-to-resource mapping lives — the Trade Catalogue is the natural home per the wireframe audit</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7011,7 +7048,7 @@
           <t>Wire the chain to refresh affected budget lines on reservation create/close, or schedule it; on-demand was the honest first cut</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7048,7 +7085,7 @@
           <t>Closed by implementation; the stewardship guidance should still cite VAL-05</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -7085,7 +7122,7 @@
           <t>Add period-from/to to request lines when planning dates exist, and price estTotal as qty x rate x days</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7122,7 +7159,7 @@
           <t>Decide what a re-import should mean: refuse, update the header, or reconcile the WBS tree adding and flagging removals. Reconciliation is the one planners will expect and the one that can silently orphan budget lines</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7159,7 +7196,7 @@
           <t>Confirm the boundary: does KONSTRYX ever need activity-level data, or does it stop at WBS?</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7196,7 +7233,7 @@
           <t>Add a startup check that counts loaded rows against the file and fails loudly on a mismatch. Same class of problem as S-05</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7233,7 +7270,7 @@
           <t>Decide per document type whether an unsynchronised project blocks creation or only release. Closes the second half of S-17</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7270,7 +7307,7 @@
           <t>Confirm whether project codes should be issued by a number range, typed, or either depending on the client</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7307,7 +7344,7 @@
           <t>Decide whether photo-heavy objects go to an object store instead. It is a per-category switch if decided before volume builds up, and a migration afterwards</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7344,7 +7381,7 @@
           <t>Add a size cap and virus scanning before the first client upload. SAP BTP has a Malware Scanning service; the size cap is configuration</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7381,7 +7418,7 @@
           <t>Block deletion of a superseded version, or of anything attached to a closed approval; mark as obsolete instead</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7418,7 +7455,7 @@
           <t>Use the same mechanism for the EC&amp;O starter pack (S-13) and for delivered personas</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8101,7 +8138,7 @@
           <t>SAP Object Store</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8134,7 +8171,7 @@
           <t>HANA LOB</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8170,7 +8207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8236,178 +8273,178 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>I-49</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CAP build</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>BudgetServiceHandler imported com.sap.cds.services.cds.CdsService, which does not exist</t>
+          <t>Every user on every tenant was greeted as the same fictional person</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Service would not compile</t>
+          <t>The screens read the signed-in user out of the UI's own JSON fixture, where it was the wireframe persona Sridhar Iyer / Plant Allocation Lead / INFC. It had no relationship to the identity the service enforces against. That is worse than showing nothing in a multi-tenant product: it invites someone to believe they are looking at their own authorization when they are looking at a mock-up, and it hid the fact that no persona is assigned to any real user</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Replaced with EventContext</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+          <t>CollaborationService.whoAmI() returns the XSUAA logon name, and the screens display that string rather than a prettier one - it is what the approval trail, the import history and every persona assignment are keyed on, so a friendlier name would mean the identity a person reads is not the identity their actions are filed under. It also reports isAdmin and hasPersona separately, because the Admin scope bypasses the permission model rather than satisfying it and no screen can infer that from the data it is shown</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-50</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>CAP build</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>pom used cds-starter-spring-boot, which carries no protocol adapter</t>
+          <t>Organizational values were shipped in a content pack, which cannot be right on more than one tenant</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>All 6 services registered but exposed ZERO HTTP endpoints, silently</t>
+          <t>Plants, purchasing organizations, profit centres, cost centres and project profiles are configuration of the customer's own S/4. The pack that seeded my434396 carried values read off my401381, and a live push came back Profit Center 10001000 does not exist - plausible values that belonged to a different system. Because packs are insert-if-missing, the tenant could not be corrected by shipping a new pack either, which is why konstryx-srv still carries eight S4_* environment overrides</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Switched to cds-starter-spring-boot-odata</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
+          <t>AdminService.syncOrgFromS4() reads them from the tenant's own S/4 through the ITS_S4 destination into an S4OrgValue mirror, and fills each company from what it finds. Catalogue reads and document reads are kept apart and marked: a catalogue proves a value exists, a live document proves it works and is the only source that says which company code uses it. It fills a blank only when exactly one value fits, overwrites only a value S/4 has never used, and reports an unmapped company rather than guessing INFC -&gt; 3310, which is a business decision and not readable</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-51</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAP build</t>
+          <t>Project Setup</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>.cdsrc.json set build.target=gen (Node layout)</t>
+          <t>A project could not be created in the product at all</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Compiled model never reached srv resources; runtime started with an empty catalogue</t>
+          <t>The Projects screen was a read-only list. Every project on every tenant arrived in a content pack or a P6 file, which makes the product a demo rather than a product - and it is why the starter-pack question could not be answered without also answering this one</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Removed; Java build now writes in place</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+          <t>ProjectService.createProject takes the header and its WBS elements in one call, with a New project dialog behind it. Together deliberately: a project with no WBS element cannot be released, so a create that stopped at the header would manufacture exactly the state PRJ-002 is stuck in - complete-looking and permanently unreleasable. releaseToS4 now pushes immediately instead of only queueing, so a project a person types reaches S/4 on one click; it still writes PENDING first and the push still refuses anything not PENDING, so the release gate is walked rather than bypassed</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-52</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>CAP build</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>CAP Java 3.5.0 rejects cds-compiler 6 from @sap/cds 9</t>
+          <t>The verification suite reached a live S/4 and started creating real projects</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Every query returned HTTP 500</t>
+          <t>Surfaced by I-51 rather than pre-existing: once release pushed on its own, the regression run began posting Enterprise Projects into whatever tenant the developer's .env named. S4Connection falls back to a gitignored .env when no destination resolves, and that file still held live my401381 credentials. Nothing was created only because the org data is now my434396's and S/4 refused with Profit Center YB101 does not exist - luck, not design</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Upgraded to cds-services 4.9.3 / Spring Boot 3.5.6</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
+          <t>S4Connection honours an S4_OFFLINE switch that short-circuits resolution before either the destination or the .env is consulted, and run_all.sh sets it. A verification run can no longer reach a tenant regardless of whose machine it runs on. The my401381 communication user still needs rotating - it transited chat transcripts (Q-09p) and is evidently still live</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>I-05</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>CAP build</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>mta.yaml declared build-result target/*-exec.jar but build produced konstryx-srv.jar</t>
+          <t>BudgetServiceHandler imported com.sap.cds.services.cds.CdsService, which does not exist</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>A Cloud Foundry deploy would have failed</t>
+          <t>Service would not compile</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Added the exec classifier</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+          <t>Replaced with EventContext</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -8421,30 +8458,30 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>I-06</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>CAP build</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>mta.yaml db-deployer pointed at gen/db, which the Java build does not produce</t>
+          <t>pom used cds-starter-spring-boot, which carries no protocol adapter</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>HDI deploy would have failed</t>
+          <t>All 6 services registered but exposed ZERO HTTP endpoints, silently</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Corrected path to db/</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+          <t>Switched to cds-starter-spring-boot-odata</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -8458,30 +8495,30 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>I-07</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Data safety</t>
+          <t>CAP build</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Demo fixtures were in db/data, which CAP deploys to every environment</t>
+          <t>.cdsrc.json set build.target=gen (Node layout)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>PRJ-001 Marina Heights would have landed in client databases</t>
+          <t>Compiled model never reached srv resources; runtime started with an empty catalogue</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Moved 13 fixtures to test/data; both config layers set; cloud profile pins initialization-mode never</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
+          <t>Removed; Java build now writes in place</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -8495,30 +8532,30 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>I-08</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>CAP build</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Proxy dropped the OData-MaxVersion header</t>
+          <t>CAP Java 3.5.0 rejects cds-compiler 6 from @sap/cds 9</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>CAP answered OData-Version 4.01; UI5 V4 model rejected the batch, table silently empty</t>
+          <t>Every query returned HTTP 500</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Proxy now forwards headers wholesale rather than by allowlist</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
+          <t>Upgraded to cds-services 4.9.3 / Spring Boot 3.5.6</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -8532,30 +8569,30 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>I-09</t>
+          <t>I-05</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Handler matched the service projection name against the persistence entity name (plural vs singular)</t>
+          <t>mta.yaml declared build-result target/*-exec.jar but build produced konstryx-srv.jar</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Handler silently protected NOTHING. Early 403s came from pre-existing service-level @requires, not from the handler</t>
+          <t>A Cloud Foundry deploy would have failed</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Resolves the projection to its source entity via CDS model reflection</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
+          <t>Added the exec classifier</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -8569,30 +8606,30 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>I-10</t>
+          <t>I-06</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>CQL.copy with a Modifier only fires where() when a WHERE already exists</t>
+          <t>mta.yaml db-deployer pointed at gen/db, which the Java build does not produce</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Unfiltered list requests — the common case — passed through unrestricted</t>
+          <t>HDI deploy would have failed</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Switched to Select.copy with an explicit predicate</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+          <t>Corrected path to db/</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -8606,30 +8643,30 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>I-07</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Data safety</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Select.where() replaced rather than ANDed the caller's filter</t>
+          <t>Demo fixtures were in db/data, which CAP deploys to every environment</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>User $filter was discarded; more rows returned than requested</t>
+          <t>PRJ-001 Marina Heights would have landed in client databases</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Existing predicate now combined explicitly with CQL.and</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+          <t>Moved 13 fixtures to test/data; both config layers set; cloud profile pins initialization-mode never</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -8643,30 +8680,30 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>I-12</t>
+          <t>I-08</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>mta.yaml had no approuter, so nothing a browser could reach</t>
+          <t>Proxy dropped the OData-MaxVersion header</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>The project had never produced a deployable archive</t>
+          <t>CAP answered OData-Version 4.01; UI5 V4 model rejected the batch, table silently empty</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Approuter added with XSUAA login and token forwarding; mbt build now produces konstryx_0.1.0.mtar (68.9 MB) with the exec jar, router, 234 HDI artifacts and xs-security.json</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
+          <t>Proxy now forwards headers wholesale rather than by allowlist</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -8680,32 +8717,32 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>I-24</t>
+          <t>I-09</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>No BTP target available for KONSTRYX</t>
+          <t>Handler matched the service projection name against the persistence entity name (plural vs singular)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>The CF CLI is targeted at an unrelated client subaccount (LAND MARK INTERNATIONAL) and its token has expired. The archive is built but cannot be pushed</t>
+          <t>Handler silently protected NOTHING. Early 403s came from pre-existing service-level @requires, not from the handler</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Needs a KONSTRYX subaccount with Cloud Foundry, HANA Cloud and XSUAA entitlements, and a fresh cf login</t>
+          <t>Resolves the projection to its source entity via CDS model reflection</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -8717,32 +8754,32 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>I-13</t>
+          <t>I-10</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Demo data</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Wireframe request header (716,044) does not reconcile with its own line values (685,080)</t>
+          <t>CQL.copy with a Modifier only fires where() when a WHERE already exists</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Any stakeholder demo shows inconsistent totals</t>
+          <t>Unfiltered list requests — the common case — passed through unrestricted</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Switched to Select.copy with an explicit predicate</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -8754,32 +8791,32 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>I-14</t>
+          <t>I-11</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Personalization, attachments and approvals on every object were not in the 22-week MVP estimate</t>
+          <t>Select.where() replaced rather than ANDed the caller's filter</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Plan credibility; 434 screens each inherit this layer</t>
+          <t>User $filter was discarded; more rows returned than requested</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Existing predicate now combined explicitly with CQL.and</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -8791,32 +8828,32 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>I-15</t>
+          <t>I-12</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Admin persona cannot read workflow/project services</t>
+          <t>mta.yaml had no approuter, so nothing a browser could reach</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Service-level @requires still gates entry by XSUAA role; the Admin mock user lacks those roles</t>
+          <t>The project had never produced a deployable archive</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>By design today, but role collections need reviewing before go-live</t>
+          <t>Approuter added with XSUAA login and token forwarding; mbt build now produces konstryx_0.1.0.mtar (68.9 MB) with the exec jar, router, 234 HDI artifacts and xs-security.json</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -8828,32 +8865,32 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>I-17</t>
+          <t>I-24</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Enforcement broke every worklist request with HTTP 500</t>
+          <t>No BTP target available for KONSTRYX</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>The handler filters on catalogue paths project.code and company.code, but RequestOverview is a grouped projection that exposed projectCode as a flat string and dropped both associations. Missed because enforcement was verified against the service directly and the UI was not re-tested after</t>
+          <t>The CF CLI is targeted at an unrelated client subaccount (LAND MARK INTERNATIONAL) and its token has expired. The archive is built but cannot be pushed</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>View now exposes the project and company associations. Worth adding a startup check that every declared path resolves on every projection, so this fails at boot rather than per request</t>
+          <t>Needs a KONSTRYX subaccount with Cloud Foundry, HANA Cloud and XSUAA entitlements, and a fresh cf login</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -8865,30 +8902,30 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>I-18</t>
+          <t>I-13</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Demo data</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Local FLP sandbox does not boot</t>
+          <t>Wireframe request header (716,044) does not reconcile with its own line values (685,080)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>flp.html fails with 'Cannot read properties of null (reading src)'. sandbox2 is deprecated since 1.136 and the newer sap/ushell/sandbox boot contract differs</t>
+          <t>Any stakeholder demo shows inconsistent totals</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Open — either finish the sandbox boot or verify launchpad integration directly on BTP</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8902,32 +8939,32 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>I-16</t>
+          <t>I-14</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Upgrade safety</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Client configuration in db/data is reset on every upgrade</t>
+          <t>Personalization, attachments and approvals on every object were not in the 22-week MVP estimate</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>cds build --production generates konstryx.nr-NumberRangeObject.hdbtabledata. HDI re-imports managed rows on redeploy, so a client who changes a number range scope or pattern would silently have it reverted at the next upgrade</t>
+          <t>Plan credibility; 434 screens each inherit this layer</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Fixed: configurable content moved to versioned packs applied insert-if-missing. Proven — client re-scoped RR to COMPANY, an upgrade pack containing an RR row was applied, RR kept the client's scope and only the new row arrived</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -8939,32 +8976,32 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>I-19</t>
+          <t>I-15</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Content packs</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Packs applied in filename order, not version order</t>
+          <t>Admin persona cannot read workflow/project services</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>number-ranges-v2.json sorted before number-ranges.json because '-' precedes '.', so 1.0.1 applied before 1.0.0 and the base pack reported its own rows as pre-existing</t>
+          <t>Service-level @requires still gates entry by XSUAA role; the Admin mock user lacks those roles</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Sort by packId then zero-padded version segments, so 1.0.10 follows 1.0.9</t>
+          <t>By design today, but role collections need reviewing before go-live</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -8976,30 +9013,30 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>I-29</t>
+          <t>I-17</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>ProjectService dropped associations to master data</t>
+          <t>Enforcement broke every worklist request with HTTP 500</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>CAP omits an association whose target is not exposed in the same service, so a project CBS node could not say which library node it came from and a planned resource could not name its resource. ProjectResources was unusable in a UI</t>
+          <t>The handler filters on catalogue paths project.code and company.code, but RequestOverview is a grouped projection that exposed projectCode as a flat string and dropped both associations. Missed because enforcement was verified against the service directly and the UI was not re-tested after</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Expose ResourceCatalog and CBSLibrary read-only in ProjectService for resolution; maintenance stays in MasterDataService</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
+          <t>View now exposes the project and company associations. Worth adding a startup check that every declared path resolves on every projection, so this fails at boot rather than per request</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9013,32 +9050,32 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>I-27</t>
+          <t>I-18</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Test data</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Seed data violated the model's own hierarchy rule</t>
+          <t>Local FLP sandbox does not boot</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Every resource was an L5 with no parent, so activation failed with 'L5 needs a parent at L4' and no seeded master could be edited or saved. 'Below this node' was empty on every page</t>
+          <t>flp.html fails with 'Cannot read properties of null (reading src)'. sandbox2 is deprecated since 1.136 and the newer sap/ushell/sandbox boot contract differs</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Replaced with a real L1-L5 tree of 28 nodes, leaf IDs preserved so rates and request lines still resolve</t>
+          <t>Open — either finish the sandbox boot or verify launchpad integration directly on BTP</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -9050,257 +9087,257 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>I-40</t>
+          <t>I-16</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Upgrade safety</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>The first real Cloud Foundry deployment: six blockers, none reachable by the test suite</t>
+          <t>Client configuration in db/data is reset on every upgrade</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>KONSTRYX had never been deployed. mta.yaml, the db module and the cloud Spring profile were all written ahead of ever being run, and each was wrong in a way only execution could expose. In order: (1) the subaccount lacked the SAP HANA Schemas &amp; HDI Containers entitlement, so service plan hdi-shared did not exist - you added it; (2) db/ had no package.json at all, so the HDI deployer task died on npm ENOENT every attempt; (3) that same missing file made mbt's npm install --production walk UP to the repo root and prune it, deleting @sap/cds-dk and breaking the NEXT maven build with 'cds is not recognized' in a module nobody had touched; (4) the start script carried --use-hdb-container-key, a 4.x-only flag removed in hdi-deploy 5; (5) hdi-deploy 5 needs @sap/hana-client as a peer where 4.x bundled a driver; (6) the cloud profile declared cds.remote.services for S4/ARIBA/SF with no EDMX imported and no consumer, so the Java service crash-looped on CdsDefinitionNotFoundException</t>
+          <t>cds build --production generates konstryx.nr-NumberRangeObject.hdbtabledata. HDI re-imports managed rows on redeploy, so a client who changes a number range scope or pattern would silently have it reverted at the next upgrade</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>All fixed and committed. Deployment succeeds: HDI reports 243 files deployed / 0 warnings, konstryx-srv connects to HANA and starts in 5.5s, srv and approuter both 1/1, OData returns 401 unauthenticated and the approuter 302s into the XSUAA login</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
+          <t>Fixed: configurable content moved to versioned packs applied insert-if-missing. Proven — client re-scoped RR to COMPANY, an upgrade pack containing an RR row was applied, RR kept the client's scope and only the new row arrived</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>B-10</t>
+          <t>I-19</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Content packs</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>The S/4 connection runs through the ITS_S4 destination</t>
+          <t>Packs applied in filename order, not version order</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>S4Connection read S4_HOST / S4_USER / S4_PASSWORD straight from the environment on EVERY environment, Cloud Foundry included. Its own class comment claimed the destination service would replace it in production - the seam was described but never built, so a deployed instance would have needed a communication-user password in its environment, and rotating that user meant a redeploy. Ziya named ITS_S4 as the destination on 2026-08-17 and it had stayed open since</t>
+          <t>number-ranges-v2.json sorted before number-ranges.json because '-' precedes '.', so 1.0.1 applied before 1.0.0 and the base pack reported its own rows as pre-existing</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Resolves the destination by name through the Cloud SDK (DestinationAccessor), overridable per environment with S4_DESTINATION, falling back to the .env path only where no destination service is bound. Destination headers are asked for PER REQUEST rather than cached: for Basic authentication that changes nothing, but for OAuth the SDK is minting and refreshing a token behind the call and a cached header would work exactly until the first expiry. Resolution moved to startup so the log states which mode an instance is in - the first question anyone asks when a sync misbehaves, and a lazily-resolved connection only answers it after something has already gone wrong. Both connectors are untouched: they get requests executed, never credentials</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Done - the fallback path; the destination path is unverified</t>
+          <t>Sort by packId then zero-padded version segments, so 1.0.10 follows 1.0.9</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Both branches of the resolver verified live at startup: the local run logs 'Destination ITS_S4 did not resolve (DestinationNotFoundException); falling back to the local environment' followed by 'S/4 connection configured locally for https://my401381-api.s4hana.cloud.sap', which is the expected pair on a machine with no destination service. Full regression 15 suites / 424 checks green</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>THE DESTINATION BRANCH HAS NOT RUN. It cannot be exercised locally - there is no destination service to bind - and deployment is paused, so the first real test is the next deploy. mta.yaml already binds konstryx-srv to konstryx-destination, so no descriptor change was needed; the destination itself must be created in the SUBACCOUNT, never in mta.yaml, because a destination declared in the descriptor would put a communication-user password in the repository</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>I-47</t>
+          <t>I-29</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>The MTA build shipped a week-old database schema, and HDI deployed it happily</t>
+          <t>ProjectService dropped associations to master data</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>The konstryx-db-deployer module had no build step, so mbt packaged whatever db/src/gen already contained. That directory was last generated on 17 Aug. Five days of model changes - s4Material on ResourceNode (I-35), then s4ServiceProduct and the RateMaster routing columns (I-44) - never reached HANA. HDI deployed the stale artifacts, reported the task SUCCEEDED, and the service then failed every read of konstryx.master.ResourceNode with 'invalid column name: T0.S4MATERIAL_ID', which took down the whole MASTER_DATA content pack. Nothing in the build or the deploy said anything was wrong: a stale generated artifact deploys perfectly, and it is the application that breaks, later, somewhere else</t>
+          <t>CAP omits an association whose target is not exposed in the same service, so a project CBS node could not say which library node it came from and a planned resource could not name its resource. ProjectResources was unusable in a UI</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>mta.yaml now runs `npx cds build --production` as the db module's build command, so the HDI artifacts are regenerated from the current model on every build and cannot drift again. Verified by extracting the hdbtable out of the built mtar before deploying, not by trusting the build log</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
+          <t>Expose ResourceCatalog and CBSLibrary read-only in ProjectService for resolution; maintenance stays in MasterDataService</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>I-48</t>
+          <t>I-27</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Test data</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Wiring the destination loader crash-looped the service on a version clash</t>
+          <t>Seed data violated the model's own hierarchy rule</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>connectivity-destination-service is genuinely required - cloudplatform-connectivity gives you the DestinationAccessor API but registers only EnvVarDestinationLoader, so ITS_S4 could never resolve however well the subaccount was configured. Adding it dragged com.sap.cloud.security java-security / java-api / env from 3.7.4 to 4.0.7 by nearest-wins, while CAP's own spring-security stayed at 3.7.4 and calls JwtValidatorBuilder.withHttpClient(CloseableHttpClient), which 4.0.7 removed. The failure named neither the dependency nor the destination: it was a NoSuchMethodError during Spring Security bean creation, and it crash-looped konstryx-srv on a live space</t>
+          <t>Every resource was an L5 with no parent, so activation failed with 'L5 needs a parent at L4' and no seeded master could be edited or saved. 'Below this node' was empty on every page</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Reverted first to restore service, diagnosed with `mvn -pl srv dependency:tree`, then fixed forward: dependencyManagement pins those three artifacts to the 3.7.4 line CAP is built against. Also widened S4Connection's resolver to catch LinkageError as well as RuntimeException - reaching S/4 is optional infrastructure and a classpath fault in it must degrade the connection to unconfigured, never take the service down. The crash was not a total loss: before dying, that build logged 'S/4 connection uses destination ITS_S4 -&gt; https://my434396-api.s4hana.cloud.sap', which is how we know the destination exists and the loader works</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
+          <t>Replaced with a real L1-L5 tree of 28 nodes, leaf IDs preserved so rates and request lines still resolve</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>I-49</t>
+          <t>I-40</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>The requisition payload named three things S/4 does not call by those names</t>
+          <t>The first real Cloud Foundry deployment: six blockers, none reachable by the test suite</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Once SAP_COM_0102 was activated, the connector was checked against the tenant's own $metadata instead of against documentation. The V4 shape was right - ISO dates, navigation properties, a top-level response - and so was the service path, every header property and all eleven item properties. Three names were wrong: the entity set is PurchaseReqn not PurchaseRequisition, the item-to-account navigation is _PurchaseReqnAcctAssgmt not _PurReqnAcctAssgmt, and the account property is PurchaseReqnAcctAssgmtNumber not PurReqnAcctAssgmtNumber. Note the trap: the header-to-item navigation really IS spelled out as _PurchaseRequisitionItem while its sibling is abbreviated, so guessing consistently would have got one of the two wrong whichever way it guessed</t>
+          <t>KONSTRYX had never been deployed. mta.yaml, the db module and the cloud Spring profile were all written ahead of ever being run, and each was wrong in a way only execution could expose. In order: (1) the subaccount lacked the SAP HANA Schemas &amp; HDI Containers entitlement, so service plan hdi-shared did not exist - you added it; (2) db/ had no package.json at all, so the HDI deployer task died on npm ENOENT every attempt; (3) that same missing file made mbt's npm install --production walk UP to the repo root and prune it, deleting @sap/cds-dk and breaking the NEXT maven build with 'cds is not recognized' in a module nobody had touched; (4) the start script carried --use-hdb-container-key, a 4.x-only flag removed in hdi-deploy 5; (5) hdi-deploy 5 needs @sap/hana-client as a peer where 4.x bundled a driver; (6) the cloud profile declared cds.remote.services for S4/ARIBA/SF with no EDMX imported and no consumer, so the Java service crash-looped on CdsDefinitionNotFoundException</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Corrected. Read via S4Probe, a read-only startup probe added for the purpose: the credentials that work live in the ITS_S4 destination on the deployed app, not on a developer machine, so the metadata had to be read from there. It is gated on the S4_PROBE environment variable - set it, restart, read the log, unset it - and only ever issues a GET. Two things it taught along the way: S/4 answers $metadata with 406 if the Accept header asks for JSON only, which reads exactly like a wrong service path; and an EntitySet and its EntityType do not share a name (PurchaseReqn vs PurchaseReqnType), so the probe now discovers the type names rather than assuming them</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
+          <t>All fixed and committed. Deployment succeeds: HDI reports 243 files deployed / 0 warnings, konstryx-srv connects to HANA and starts in 5.5s, srv and approuter both 1/1, OData returns 401 unauthenticated and the approuter 302s into the XSUAA login</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>I-43</t>
+          <t>B-10</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>The requisition push targeted the wrong API and the wrong communication scenario</t>
+          <t>The S/4 connection runs through the ITS_S4 destination</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Built on 2026-08-19 against API_PURCHASEREQ_PROCESS_SRV under SAP_COM_0053, both carried forward from an older working note rather than checked. The consolidated requirements V02 §15.2 row 9 and RB-145 put the requisition on API_PURCHASEREQUISITION_2 under SAP_COM_0102. SAP_COM_0053 appears 22 times in V02 and is attached to the PURCHASE ORDER every single time, never to a requisition — so the connector would have been pointed at the order scenario. Worse for the record, SAP_COM_0193, which the tracker and the project memory both cited for the order, appears NOWHERE in V02; it was invented somewhere upstream and repeated</t>
+          <t>S4Connection read S4_HOST / S4_USER / S4_PASSWORD straight from the environment on EVERY environment, Cloud Foundry included. Its own class comment claimed the destination service would replace it in production - the seam was described but never built, so a deployed instance would have needed a communication-user password in its environment, and rotating that user meant a redeploy. Ziya named ITS_S4 as the destination on 2026-08-17 and it had stayed open since</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Connector repointed. The API change is not just a rename: API_PURCHASEREQUISITION_2 is the V4-generation API, so the payload moved from V2 conventions (/Date(millis)/ dates, to_ navigation sets, a d-wrapped response) to V4 (ISO dates, _-prefixed navigation properties, a top-level response), and the error reader now handles both shapes. The service root is env-overridable via S4_PR_SERVICE because it is the single most likely thing still to be wrong. Docs corrected in the same pass, including the scenario table that carried SAP_COM_0193</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t>Resolves the destination by name through the Cloud SDK (DestinationAccessor), overridable per environment with S4_DESTINATION, falling back to the .env path only where no destination service is bound. Destination headers are asked for PER REQUEST rather than cached: for Basic authentication that changes nothing, but for OAuth the SDK is minting and refreshing a token behind the call and a cached header would work exactly until the first expiry. Resolution moved to startup so the log states which mode an instance is in - the first question anyone asks when a sync misbehaves, and a lazily-resolved connection only answers it after something has already gone wrong. Both connectors are untouched: they get requests executed, never credentials</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Done - the fallback path; the destination path is unverified</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>Both branches of the resolver verified live at startup: the local run logs 'Destination ITS_S4 did not resolve (DestinationNotFoundException); falling back to the local environment' followed by 'S/4 connection configured locally for https://my401381-api.s4hana.cloud.sap', which is the expected pair on a machine with no destination service. Full regression 15 suites / 424 checks green</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>THE DESTINATION BRANCH HAS NOT RUN. It cannot be exercised locally - there is no destination service to bind - and deployment is paused, so the first real test is the next deploy. mta.yaml already binds konstryx-srv to konstryx-destination, so no descriptor change was needed; the destination itself must be created in the SUBACCOUNT, never in mta.yaml, because a destination declared in the descriptor would put a communication-user password in the repository</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>I-44</t>
+          <t>I-47</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Master data</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Only a material could be ordered, so nothing hired could be</t>
+          <t>The MTA build shipped a week-old database schema, and HDI deployed it happily</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>ResourceNode carried s4Material and nothing else, which meant a requisition line could name a product to buy and nothing else. Every non-material class was therefore unorderable: a hired crane, labour supplied by an LSC, a subcontracted package. The consolidated requirements make this a first-class rule — spec §8 / principle P10, class routes the leaf to S/4 — and state the consequence plainly: a leaf that carries neither an activity type nor a service product cannot be costed, and one carrying both without declaring which applies will be costed twice. The 2026-08-17 ruling of material-number-only predates V02 and was made against the v12 masters screen, which does not show this</t>
+          <t>The konstryx-db-deployer module had no build step, so mbt packaged whatever db/src/gen already contained. That directory was last generated on 17 Aug. Five days of model changes - s4Material on ResourceNode (I-35), then s4ServiceProduct and the RateMaster routing columns (I-44) - never reached HANA. HDI deployed the stale artifacts, reported the task SUCCEEDED, and the service then failed every read of konstryx.master.ResourceNode with 'invalid column name: T0.S4MATERIAL_ID', which took down the whole MASTER_DATA content pack. Nothing in the build or the deploy said anything was wrong: a stale generated artifact deploys perfectly, and it is the application that breaks, later, somewhere else</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Split across the two places the wireframe itself splits it, which turns out to preserve the original ruling rather than overturn it — one material per resource still holds, because a material is source-independent. (1) ResourceNode.s4ServiceProduct: the GENERIC service product, what a requisition orders, because a requisition is raised before a vendor exists and naming one vendor catalogue code on a pre-award document would pre-decide the award. (2) RateMaster gains source (IN_HOUSE / HIRED / LSC_HIRED), vendor, s4ActivityType and s4ServiceProduct: what a COST posts against. Source is the declaration that stops double-costing — in-house carries an activity type and no vendor, hired carries a vendor and that vendor own service product, and a row carrying both is refused. raisePurchaseRequisition now resolves by class: MR takes the material, everything else takes the service product</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
+          <t>mta.yaml now runs `npx cds build --production` as the db module's build command, so the HDI artifacts are regenerated from the current model on every build and cannot drift again. Verified by extracting the hdbtable out of the built mtar before deploying, not by trusting the build log</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9314,30 +9351,30 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>I-45</t>
+          <t>I-48</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Master data</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>The rate uniqueness rule would have refused the product's own specified data</t>
+          <t>Wiring the destination loader crash-looped the service on a version clash</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Rates were unique on resource + effectiveFrom + scope. The wireframe's manpower master lists MP-CIV-CAR-SK-G1 three times on the same day at three rates — our payroll at AED 28.50/hr, Alpha Civil at 24.00, Beta Labour at 23.50 — because a rate is not a property of the resource alone. Keying on resource would have called two of those a duplicate and refused them. Found while adding source and vendor, not by a failing test: nothing had ever tried to seed the second row</t>
+          <t>connectivity-destination-service is genuinely required - cloudplatform-connectivity gives you the DestinationAccessor API but registers only EnvVarDestinationLoader, so ITS_S4 could never resolve however well the subaccount was configured. Adding it dragged com.sap.cloud.security java-security / java-api / env from 3.7.4 to 4.0.7 by nearest-wins, while CAP's own spring-security stayed at 3.7.4 and calls JwtValidatorBuilder.withHttpClient(CloseableHttpClient), which 4.0.7 removed. The failure named neither the dependency nor the destination: it was a NoSuchMethodError during Spring Security bean creation, and it crash-looped konstryx-srv on a live space</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Key widened to resource + source + vendor + effectiveFrom + scope. The seeded fixture now carries the in-house and Alpha Civil rows on the same day, which is the case the old rule rejected, and test_rates asserts both survive as well as asserting the narrow duplicate is still a 409</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
+          <t>Reverted first to restore service, diagnosed with `mvn -pl srv dependency:tree`, then fixed forward: dependencyManagement pins those three artifacts to the 3.7.4 line CAP is built against. Also widened S4Connection's resolver to catch LinkageError as well as RuntimeException - reaching S/4 is optional infrastructure and a classpath fault in it must degrade the connection to unconfigured, never take the service down. The crash was not a total loss: before dying, that build logged 'S/4 connection uses destination ITS_S4 -&gt; https://my434396-api.s4hana.cloud.sap', which is how we know the destination exists and the loader works</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9351,30 +9388,30 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>I-46</t>
+          <t>I-49</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>The persona that maintains rates could not see what a rate now names</t>
+          <t>The requisition payload named three things S/4 does not call by those names</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>A consequence of I-44 rather than a pre-existing defect. Once a rate names the vendor whose contract it belongs to and the S/4 service product it is procured against, the master-data steward has to be able to read both to maintain one — and MD_STEWARD had full CRUD on KX_RATE but no grant at all on KX_VENDOR or KX_MATERIAL. Surfaced as a 403 in the new test, not by inspection</t>
+          <t>Once SAP_COM_0102 was activated, the connector was checked against the tenant's own $metadata instead of against documentation. The V4 shape was right - ISO dates, navigation properties, a top-level response - and so was the service path, every header property and all eleven item properties. Three names were wrong: the entity set is PurchaseReqn not PurchaseRequisition, the item-to-account navigation is _PurchaseReqnAcctAssgmt not _PurReqnAcctAssgmt, and the account property is PurchaseReqnAcctAssgmtNumber not PurReqnAcctAssgmtNumber. Note the trap: the header-to-item navigation really IS spelled out as _PurchaseRequisitionItem while its sibling is abbreviated, so guessing consistently would have got one of the two wrong whichever way it guessed</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Granted activity 03 (display) on both, and only 03: they are S/4 mirrors, and DM-01 says a mirror is not ours to edit. PERSONAS content pack bumped 1.0.0 to 1.1.0 so an existing installation picks the grants up</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
+          <t>Corrected. Read via S4Probe, a read-only startup probe added for the purpose: the credentials that work live in the ITS_S4 destination on the deployed app, not on a developer machine, so the metadata had to be read from there. It is gated on the S4_PROBE environment variable - set it, restart, read the log, unset it - and only ever issues a GET. Two things it taught along the way: S/4 answers $metadata with 406 if the Accept header asks for JSON only, which reads exactly like a wrong service path; and an EntitySet and its EntityType do not share a name (PurchaseReqn vs PurchaseReqnType), so the probe now discovers the type names rather than assuming them</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9388,7 +9425,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>I-42</t>
+          <t>I-43</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -9398,182 +9435,182 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Every WBS element pushed to S/4 forgot what S/4 called it</t>
+          <t>The requisition push targeted the wrong API and the wrong communication scenario</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>S4ProjectConnector created each WBS element under the project and threw the response away, counting successes and failures but recording neither key. WBSElement carries the s4outbound aspect, so it HAS an s4Key field - it was simply never written, on any row, since the connector was built. Nothing noticed because the only consumer until now was the project header, which does record its own key. It surfaced the moment the requisition push needed to name the account assignment: the WBS element as S/4 knows it</t>
+          <t>Built on 2026-08-19 against API_PURCHASEREQ_PROCESS_SRV under SAP_COM_0053, both carried forward from an older working note rather than checked. The consolidated requirements V02 §15.2 row 9 and RB-145 put the requisition on API_PURCHASEREQUISITION_2 under SAP_COM_0102. SAP_COM_0053 appears 22 times in V02 and is attached to the PURCHASE ORDER every single time, never to a requisition — so the connector would have been pointed at the order scenario. Worse for the record, SAP_COM_0193, which the tracker and the project memory both cited for the order, appears NOWHERE in V02; it was invented somewhere upstream and repeated</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>The connector now records each element's key from S/4's own response body, plus SENT/FAILED and the refusal text, incrementing that element's own syncAttempts. Deliberately NOT re-derived from the KONSTRYX code by repeating the connector's normalising rule - a second copy of that rule would be a guess the moment S/4 truncated or renamed anything. The requisition push refuses a line whose WBS has no key rather than inventing one</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
+          <t>Connector repointed. The API change is not just a rename: API_PURCHASEREQUISITION_2 is the V4-generation API, so the payload moved from V2 conventions (/Date(millis)/ dates, to_ navigation sets, a d-wrapped response) to V4 (ISO dates, _-prefixed navigation properties, a top-level response), and the error reader now handles both shapes. The service root is env-overridable via S4_PR_SERVICE because it is the single most likely thing still to be wrong. Docs corrected in the same pass, including the scenario table that carried SAP_COM_0193</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>I-41</t>
+          <t>I-44</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Master data</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>The deployed app serves no UI - the jar carries none</t>
+          <t>Only a material could be ordered, so nothing hired could be</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Confirmed against the built artifact rather than inferred: jar tf konstryx-srv-exec.jar lists 57 service classes and zero UI assets. mta.yaml's comment claims konstryx-srv already serves the SAPUI5 app as static content, which is not true - there is no srv/src/main/resources/static and no copy step in srv/pom.xml. Separately index.html bootstraps UI5 from a relative resources/sap-ui-core.js, which serve.py proxies to a runtime on the developer's local disk and which nothing serves in CF. The approuter's /konstryx-ui/* route forwards to a service with nothing behind it</t>
+          <t>ResourceNode carried s4Material and nothing else, which meant a requisition line could name a product to buy and nothing else. Every non-material class was therefore unorderable: a hired crane, labour supplied by an LSC, a subcontracted package. The consolidated requirements make this a first-class rule — spec §8 / principle P10, class routes the leaf to S/4 — and state the consequence plainly: a leaf that carries neither an activity type nor a service product cannot be costed, and one carrying both without declaring which applies will be costed twice. The 2026-08-17 ruling of material-number-only predates V02 and was made against the v12 masters screen, which does not show this</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Open - this is Q-11. html5-apps-repo IS entitled in this space, which is the clean answer: build the UI as its own MTA module into the HTML5 application repository rather than packaging it into the Java jar. The launchpad tile (semantic object + action, per your ruling) needs this finished behind it or the tile launches a 404</t>
+          <t>Split across the two places the wireframe itself splits it, which turns out to preserve the original ruling rather than overturn it — one material per resource still holds, because a material is source-independent. (1) ResourceNode.s4ServiceProduct: the GENERIC service product, what a requisition orders, because a requisition is raised before a vendor exists and naming one vendor catalogue code on a pre-award document would pre-decide the award. (2) RateMaster gains source (IN_HOUSE / HIRED / LSC_HIRED), vendor, s4ActivityType and s4ServiceProduct: what a COST posts against. Source is the declaration that stops double-costing — in-house carries an activity type and no vendor, hired carries a vendor and that vendor own service product, and a row carrying both is refused. raisePurchaseRequisition now resolves by class: MR takes the material, everything else takes the service product</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>I-35</t>
+          <t>I-45</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Master data</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>A resource has no S/4 material number, so a requisition cannot name what to buy</t>
+          <t>The rate uniqueness rule would have refused the product's own specified data</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>master.ResourceNode is the KONSTRYX resource code (L1-L5) and master.Material is the separate S/4 product mirror, but nothing links them — ResourceNode has no material field and Material has no resource field. The requisition therefore carries the resource and its description, which is enough for the KONSTRYX side but not enough to POST to API_PURCHASEREQ_PROCESS_SRV, which needs the S/4 material number. The wireframe already shows this mapping existing (masters.html renders resource rows with an S/4 material column, e.g. MAT-STL-SS316-12 against 100024780), so the intent is there and only the model is missing</t>
+          <t>Rates were unique on resource + effectiveFrom + scope. The wireframe's manpower master lists MP-CIV-CAR-SK-G1 three times on the same day at three rates — our payroll at AED 28.50/hr, Alpha Civil at 24.00, Beta Labour at 23.50 — because a rate is not a property of the resource alone. Keying on resource would have called two of those a duplicate and refused them. Found while adding source and vendor, not by a failing test: nothing had ever tried to seed the second row</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Parked by you 2026-08-17 so PO work could continue, then answered the same day: ONE MATERIAL PER RESOURCE, not one per company. The group is on a single S/4 client, where a material number is client-level — every company code sees the same number and only the plant and valuation extensions differ — and where a company genuinely buys a different item, that item is already its own COMPANY-scoped leaf, so the hierarchy carries the company dimension without repeating it. Built: ResourceNode.s4Material, an association to the Material mirror (a reference, never a master — materials are created in S/4 and registered here). raisePurchaseRequisition resolves it onto the line when the requisition is raised rather than at push, so remapping a resource later cannot silently change what an already-open requisition buys; a resource with no material leaves the line empty rather than guessing. Scope held to the material number — the wireframe's CO activity type, SAP material type and material group are not modelled until something consumes them</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
+          <t>Key widened to resource + source + vendor + effectiveFrom + scope. The seeded fixture now carries the in-house and Alpha Civil rows on the same day, which is the case the old rule rejected, and test_rates asserts both survive as well as asserting the narrow duplicate is still a 409</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>I-36</t>
+          <t>I-46</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Every Decimal action parameter was unpostable from the UI — including on already-shipped buttons</t>
+          <t>The persona that maintains rates could not see what a rate now names</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Previously recorded as a narrow quirk of Decimals nested inside array-of-complex-type parameters (I found it on distributeToWBS's weight). It is far broader: SAPUI5's v4 ODataModel always negotiates IEEE754Compatible=true and sends Decimals as bare JSON numbers, while CAP Java's action-parameter deserialiser does the opposite of what that flag promises — it accepts a Decimal only as a quoted string when the flag is set, and only as a bare number when it is absent. So the typed setParameter path fails for ANY Decimal parameter. Confirmed by curl in all three combinations. This was silently breaking the Generate Build-up button on both Cost Mapping and Project BOQ (difficultyPct) — shipped, believed working, and never exercised through the UI</t>
+          <t>A consequence of I-44 rather than a pre-existing defect. Once a rate names the vendor whose contract it belongs to and the S/4 service product it is procured against, the master-data steward has to be able to read both to maintain one — and MD_STEWARD had full CRUD on KX_RATE but no grant at all on KX_VENDOR or KX_MATERIAL. Surfaced as a 403 in the new test, not by inspection</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>All Decimal-carrying actions now post as a raw authenticated fetch with a plain application/json content type (no IEEE754Compatible), which is why the original distributeToWBS workaround worked — not because it avoided array nesting</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
+          <t>Granted activity 03 (display) on both, and only 03: they are S/4 mirrors, and DM-01 says a mirror is not ours to edit. PERSONAS content pack bumped 1.0.0 to 1.1.0 so an existing installation picks the grants up</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>I-37</t>
+          <t>I-42</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Four list-binding traps that silently showed stale or wrong data</t>
+          <t>Every WBS element pushed to S/4 forgot what S/4 called it</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Found while building the Budget screens, each verified live rather than reasoned about. (1) OData v4 cannot expand or dot-navigate an association whose target is not exposed in the SAME service — Budgets.project and BudgetLine.cbs both cross a service boundary, and the failed expand poisoned the whole $batch so unrelated tables rendered empty. (2) A formatter that reads external JS state never re-runs when that state loads later; the CBS column stuck on raw GUIDs and neither refresh() nor checkUpdate fixed it. (3) oBinding.filter() with an unchanged filter array is a no-op that skips the server round trip entirely, so tables did not pick up rows an action had just created. (4) attachEventOnce('dataReceived') attached AFTER filter/refresh gets fired by an in-flight earlier response while the new rows are still empty, leaving counts and KPIs stuck at 0</t>
+          <t>S4ProjectConnector created each WBS element under the project and threw the response away, counting successes and failures but recording neither key. WBSElement carries the s4outbound aspect, so it HAS an s4Key field - it was simply never written, on any row, since the connector was built. Nothing noticed because the only consumer until now was the project header, which does record its own key. It surfaced the moment the requisition push needed to name the account assignment: the WBS element as S/4 knows it</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>(1) resolve cross-service references client-side from the foreign key; (2) put the lookup map on a JSONModel and bind it as a real second binding part; (3) always pair filter() with an explicit refresh(); (4) attach the handler before filter/refresh and read getAllCurrentContexts()</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
+          <t>The connector now records each element's key from S/4's own response body, plus SENT/FAILED and the refusal text, incrementing that element's own syncAttempts. Deliberately NOT re-derived from the KONSTRYX code by repeating the connector's normalising rule - a second copy of that rule would be a guess the moment S/4 truncated or renamed anything. The requisition push refuses a line whose WBS has no key rather than inventing one</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>I-38</t>
+          <t>I-41</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -9583,22 +9620,22 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>KPI tiles truncated real money to four characters</t>
+          <t>The deployed app serves no UI - the jar carries none</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>sap.m.NumericContent truncates its value at 4 chars by default (truncateValueTo), so a budget total of 381,600 rendered as '3816' with no ellipsis or any other sign that anything had been cut — a wrong number presented as a confident one</t>
+          <t>Confirmed against the built artifact rather than inferred: jar tf konstryx-srv-exec.jar lists 57 service classes and zero UI assets. mta.yaml's comment claims konstryx-srv already serves the SAPUI5 app as static content, which is not true - there is no srv/src/main/resources/static and no copy step in srv/pom.xml. Separately index.html bootstraps UI5 from a relative resources/sap-ui-core.js, which serve.py proxies to a runtime on the developer's local disk and which nothing serves in CF. The approuter's /konstryx-ui/* route forwards to a service with nothing behind it</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Set truncateValueTo explicitly and format the value with thousands separators before setting it</t>
+          <t>Open - this is Q-11. html5-apps-repo IS entitled in this space, which is the clean answer: build the UI as its own MTA module into the HTML5 application repository rather than packaging it into the Java jar. The launchpad tile (semantic object + action, per your ruling) needs this finished behind it or the tile launches a 404</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -9610,44 +9647,44 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>I-28</t>
+          <t>I-35</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Draft editing failed three ways</t>
+          <t>A resource has no S/4 material number, so a requisition cannot name what to buy</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>draftActivate bound against the draftEdit operation context produced nested deferred bindings; expanding associations on a draft failed with 'invalid segment' and swallowed the edit-mode switch; draftEdit refused a second draft, making a master permanently uneditable after a mid-edit tab close</t>
+          <t>master.ResourceNode is the KONSTRYX resource code (L1-L5) and master.Material is the separate S/4 product mirror, but nothing links them — ResourceNode has no material field and Material has no resource field. The requisition therefore carries the resource and its description, which is enough for the KONSTRYX side but not enough to POST to API_PURCHASEREQ_PROCESS_SRV, which needs the S/4 material number. The wireframe already shows this mapping existing (masters.html renders resource rows with an S/4 material column, e.g. MAT-STL-SS316-12 against 100024780), so the intent is there and only the model is missing</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Re-resolve the draft as an ordinary context, expand only the stored record, and resume an existing draft rather than erroring</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
+          <t>Parked by you 2026-08-17 so PO work could continue, then answered the same day: ONE MATERIAL PER RESOURCE, not one per company. The group is on a single S/4 client, where a material number is client-level — every company code sees the same number and only the plant and valuation extensions differ — and where a company genuinely buys a different item, that item is already its own COMPANY-scoped leaf, so the hierarchy carries the company dimension without repeating it. Built: ResourceNode.s4Material, an association to the Material mirror (a reference, never a master — materials are created in S/4 and registered here). raisePurchaseRequisition resolves it onto the line when the requisition is raised rather than at push, so remapping a resource later cannot silently change what an already-open requisition buys; a resource with no material leaves the line empty rather than guessing. Scope held to the material number — the wireframe's CO activity type, SAP material type and material group are not modelled until something consumes them</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>I-25</t>
+          <t>I-36</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -9657,131 +9694,131 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Blank screen after the app shell was removed</t>
+          <t>Every Decimal action parameter was unpostable from the UI — including on already-shipped buttons</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Stripping sap.tnt.ToolPage removed the control establishing layout height. UI5 injects a UIArea div that takes no height of its own, and the NavContainer below sets overflow:hidden - so every control was clipped to nothing while still reporting a correct size. DOM text, network and per-element geometry checks all passed while the screen was empty</t>
+          <t>Previously recorded as a narrow quirk of Decimals nested inside array-of-complex-type parameters (I found it on distributeToWBS's weight). It is far broader: SAPUI5's v4 ODataModel always negotiates IEEE754Compatible=true and sends Decimals as bare JSON numbers, while CAP Java's action-parameter deserialiser does the opposite of what that flag promises — it accepts a Decimal only as a quoted string when the flag is set, and only as a bare number when it is absent. So the typed setParameter path fails for ANY Decimal parameter. Confirmed by curl in all three combinations. This was silently breaking the Generate Build-up button on both Cost Mapping and Project BOQ (difficultyPct) — shipped, believed working, and never exercised through the UI</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Declared the full height chain in style.css. Found by painting a test div (which showed) and then walking the ancestor chain to #container-uiarea</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
+          <t>All Decimal-carrying actions now post as a raw authenticated fetch with a plain application/json content type (no IEEE754Compatible), which is why the original distributeToWBS workaround worked — not because it avoided array nesting</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>I-26</t>
+          <t>I-37</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>mbt build silently removes cds-dk</t>
+          <t>Four list-binding traps that silently showed stale or wrong data</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>The MTA build runs npm install --production at the root, pruning devDependencies. @sap/cds-dk goes with them and the next Maven build fails with 'cds' is not recognized</t>
+          <t>Found while building the Budget screens, each verified live rather than reasoned about. (1) OData v4 cannot expand or dot-navigate an association whose target is not exposed in the SAME service — Budgets.project and BudgetLine.cbs both cross a service boundary, and the failed expand poisoned the whole $batch so unrelated tables rendered empty. (2) A formatter that reads external JS state never re-runs when that state loads later; the CBS column stuck on raw GUIDs and neither refresh() nor checkUpdate fixed it. (3) oBinding.filter() with an unchanged filter array is a no-op that skips the server round trip entirely, so tables did not pick up rows an action had just created. (4) attachEventOnce('dataReceived') attached AFTER filter/refresh gets fired by an in-flight earlier response while the new rows are still empty, leaving counts and KPIs stuck at 0</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Run npm install after an MTA build</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
+          <t>(1) resolve cross-service references client-side from the foreign key; (2) put the lookup map on a JSONModel and bind it as a real second binding part; (3) always pair filter() with an explicit refresh(); (4) attach the handler before filter/refresh and read getAllCurrentContexts()</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>I-23</t>
+          <t>I-38</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Data model</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Self-referencing compositions crashed draft activation</t>
+          <t>KPI tiles truncated real money to four characters</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>ResourceNode, CBSNode and CBSInstance each declared children as a Composition of themselves. CAP expands compositions recursively on draft activation, so activating any hierarchy master died with a stack overflow in DraftActionsHandler. Composition also implies cascade-delete, so removing an L2 would have taken its subtree with it</t>
+          <t>sap.m.NumericContent truncates its value at 4 chars by default (truncateValueTo), so a budget total of 381,600 rendered as '3816' with no ellipsis or any other sign that anything had been cut — a wrong number presented as a confident one</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Changed to Association to many; the hierarchy is owned by parent and children are the inverse</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
+          <t>Set truncateValueTo explicitly and format the value with thousands separators before setting it</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>I-21</t>
+          <t>I-28</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Company-scoped authorization hid every group-scoped master</t>
+          <t>Draft editing failed three ways</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Scoped masters declared companyPath in the authorization catalogue, so the handler added owningCompany.code = 'INFC', which is null on every GROUP row. Each steward saw only their own local master and none of the five shared ones</t>
+          <t>draftActivate bound against the draftEdit operation context produced nested deferred bindings; expanding associations on a draft failed with 'invalid segment' and swallowed the edit-mode switch; draftEdit refused a second draft, making a master permanently uneditable after a mid-edit tab close</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>The company dimension for scoped entities now belongs to MasterScopeHandler alone; the catalogue declares no companyPath for them</t>
-        </is>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
+          <t>Re-resolve the draft as an ordinary context, expand only the stored record, and resume an existing draft rather than erroring</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9795,30 +9832,30 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>I-22</t>
+          <t>I-25</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Promotion approval threw NullPointerException</t>
+          <t>Blank screen after the app shell was removed</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Map.of rejects null values and clearing owningCompany_ID is precisely a null</t>
+          <t>Stripping sap.tnt.ToolPage removed the control establishing layout height. UI5 injects a UIArea div that takes no height of its own, and the NavContainer below sets overflow:hidden - so every control was clipped to nothing while still reporting a correct size. DOM text, network and per-element geometry checks all passed while the screen was empty</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Use a HashMap for update payloads that clear fields</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
+          <t>Declared the full height chain in style.css. Found by painting a test div (which showed) and then walking the ancestor chain to #container-uiarea</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9832,30 +9869,30 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>I-20</t>
+          <t>I-26</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Number ranges</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>A range configured on an entity without docNo would fail every create</t>
+          <t>mbt build silently removes cds-dk</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>konstryx.wf.AdvisoryDecision has no document number; the handler would have written the field regardless</t>
+          <t>The MTA build runs npm install --production at the root, pruning devDependencies. @sap/cds-dk goes with them and the next Maven build fails with 'cds' is not recognized</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Handler now skips targets with no docNo element, so a misconfiguration is ignored rather than breaking creates</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
+          <t>Run npm install after an MTA build</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9869,30 +9906,30 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>I-39</t>
+          <t>I-23</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Data model</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>An approval could be raised against an object that does not exist</t>
+          <t>Self-referencing compositions crashed draft activation</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>The target is polymorphic - an entity name and a key, not a typed association - so no foreign key would ever object. The approval would sit in an inbox indefinitely pointing at nothing</t>
+          <t>ResourceNode, CBSNode and CBSInstance each declared children as a Composition of themselves. CAP expands compositions recursively on draft activation, so activating any hierarchy master died with a stack overflow in DraftActionsHandler. Composition also implies cascade-delete, so removing an L2 would have taken its subtree with it</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Submission now checks the entity is in the model and the row is really there</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
+          <t>Changed to Association to many; the hierarchy is owned by parent and children are the inverse</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9906,30 +9943,30 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>I-30</t>
+          <t>I-21</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>A failing content pack left rows behind that nothing recorded as applied</t>
+          <t>Company-scoped authorization hid every group-scoped master</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Rows were inserted one at a time and the pack's own record written last. When that record failed - a description longer than its column - the rows stayed and the pack looked unapplied</t>
+          <t>Scoped masters declared companyPath in the authorization catalogue, so the handler added owningCompany.code = 'INFC', which is null on every GROUP row. Each steward saw only their own local master and none of the five shared ones</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Each pack now applies in its own change set and is abandoned whole on failure</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
+          <t>The company dimension for scoped entities now belongs to MasterScopeHandler alone; the catalogue declares no companyPath for them</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9943,30 +9980,30 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>I-33</t>
+          <t>I-22</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Seed data</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>One duplicate key in a seed CSV loads zero rows for that entity, and only logs it at INFO</t>
+          <t>Promotion approval threw NullPointerException</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>The CSV loader cancels the whole entity's change set on a unique-constraint violation. A duplicated PersonaPermission key therefore loaded no permissions at all and every request returned 403, with nothing at WARN or ERROR explaining why</t>
+          <t>Map.of rejects null values and clearing owningCompany_ID is precisely a null</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Duplicate removed. The behaviour itself is unchanged and will recur — see S-27</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
+          <t>Use a HashMap for update payloads that clear fields</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9980,30 +10017,30 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>I-34</t>
+          <t>I-20</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Project Setup</t>
+          <t>Number ranges</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>@readonly on a projection element does not cover the draft path</t>
+          <t>A range configured on an entity without docNo would fail every create</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>CAP dispatches a draft edit as DRAFT_PATCH, which the annotation does not gate. The draft displayed syncStatus SENT and an invented S/4 key. Activation stripped them so the stored record was never wrong, but the user was shown something untrue until they saved</t>
+          <t>konstryx.wf.AdvisoryDecision has no document number; the handler would have written the field regardless</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Guarded on the draft event as well as the active one</t>
-        </is>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
+          <t>Handler now skips targets with no docNo element, so a misconfiguration is ignored rather than breaking creates</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -10017,30 +10054,30 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>I-32</t>
+          <t>I-39</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Personalization</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Every user could read and write every other user's saved layouts</t>
+          <t>An approval could be raised against an object that does not exist</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>UserVariant was modelled with a user column and no handler behind it, so nothing filtered reads and nothing stopped the payload naming a different owner. A saved filter names projects, counterparties and cost codes, so another person's variant list tells you what they work on</t>
+          <t>The target is polymorphic - an entity name and a key, not a typed association - so no foreign key would ever object. The approval would sit in an inbox indefinitely pointing at nothing</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Owner is taken from the session; reads are narrowed to own plus published; writes to someone else's answer 404 rather than 403 so the key is not confirmed</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
+          <t>Submission now checks the entity is in the model and the row is really there</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -10054,35 +10091,183 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
+          <t>I-30</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>A failing content pack left rows behind that nothing recorded as applied</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Rows were inserted one at a time and the pack's own record written last. When that record failed - a description longer than its column - the rows stayed and the pack looked unapplied</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Each pack now applies in its own change set and is abandoned whole on failure</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>I-33</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Seed data</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>One duplicate key in a seed CSV loads zero rows for that entity, and only logs it at INFO</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>The CSV loader cancels the whole entity's change set on a unique-constraint violation. A duplicated PersonaPermission key therefore loaded no permissions at all and every request returned 403, with nothing at WARN or ERROR explaining why</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Duplicate removed. The behaviour itself is unchanged and will recur — see S-27</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>I-34</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Project Setup</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>@readonly on a projection element does not cover the draft path</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>CAP dispatches a draft edit as DRAFT_PATCH, which the annotation does not gate. The draft displayed syncStatus SENT and an invented S/4 key. Activation stripped them so the stored record was never wrong, but the user was shown something untrue until they saved</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Guarded on the draft event as well as the active one</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>I-32</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Personalization</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Every user could read and write every other user's saved layouts</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>UserVariant was modelled with a user column and no handler behind it, so nothing filtered reads and nothing stopped the payload naming a different owner. A saved filter names projects, counterparties and cost codes, so another person's variant list tells you what they work on</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Owner is taken from the session; reads are narrowed to own plus published; writes to someone else's answer 404 rather than 403 so the key is not confirmed</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
           <t>I-31</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>withdraw and delegate returned 501 Not Implemented</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Both actions were declared in CDS without a return type while their handlers set one, which CAP rejects at the protocol layer rather than at build time. Only reachable by calling them - the build was clean</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Declared returns String on both</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
